--- a/Gestion Stock 2025/Gestion de Stock Berrouaghia/Suivie pose Compteur 2025.xlsx
+++ b/Gestion Stock 2025/Gestion de Stock Berrouaghia/Suivie pose Compteur 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2025\Gestion de Stock Berrouaghia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B35169-65EB-45C2-A348-957443EA663D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A62A18-07E1-4BDE-AB4D-8228B944CE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Janvier 2025" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3394" uniqueCount="1818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3395" uniqueCount="1820">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -5786,6 +5786,12 @@
   </si>
   <si>
     <t>BB0269</t>
+  </si>
+  <si>
+    <t>2025118111</t>
+  </si>
+  <si>
+    <t>BC0809</t>
   </si>
 </sst>
 </file>
@@ -8797,7 +8803,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>99</v>
+        <v>1819</v>
       </c>
       <c r="C25" s="13">
         <v>30</v>
@@ -32705,7 +32711,7 @@
       </c>
       <c r="H80" s="4"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="12">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -32730,7 +32736,7 @@
       </c>
       <c r="H81" s="4"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="12">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -32757,7 +32763,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="12">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -32769,7 +32775,7 @@
         <v>18</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>1150</v>
+        <v>1818</v>
       </c>
       <c r="E83" s="15">
         <v>45917</v>
@@ -32783,8 +32789,11 @@
       <c r="H83" s="4" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I83" s="14" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="12">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -32809,7 +32818,7 @@
       </c>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="12">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -32834,7 +32843,7 @@
       </c>
       <c r="H85" s="4"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="12">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -32859,7 +32868,7 @@
       </c>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="12">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -32884,7 +32893,7 @@
       </c>
       <c r="H87" s="4"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="12">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -32909,7 +32918,7 @@
       </c>
       <c r="H88" s="4"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="12">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -32934,7 +32943,7 @@
       </c>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="12">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -32959,7 +32968,7 @@
       </c>
       <c r="H90" s="4"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="12">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -32986,7 +32995,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="12">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -33011,7 +33020,7 @@
       </c>
       <c r="H92" s="4"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="12">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -33038,7 +33047,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="12">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -33065,7 +33074,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="12">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -33092,7 +33101,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="12">
         <f t="shared" si="1"/>
         <v>90</v>
